--- a/Output_Data/Integrated_Values/Right_Leg/Integrated_Values_Edited.xlsx
+++ b/Output_Data/Integrated_Values/Right_Leg/Integrated_Values_Edited.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,14 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Customer\Projects\MultiCam_Study\Output_Data\Integrated_Values\Right_Leg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{DE70CF79-9362-4C75-B1C4-C8AF4A5778B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AFBC41-1E90-4F6D-85A7-19C547165AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Integrated_Values" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -88,7 +100,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -225,7 +237,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -403,12 +415,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -574,7 +580,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -929,59 +935,62 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="8.88671875" style="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>0.93816496051526399</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>0.94615719726366998</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>0.87528143665927904</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <f>AVERAGE(C2:E2)</f>
         <v>0.91986786481273775</v>
       </c>
@@ -994,28 +1003,28 @@
       <c r="I2" s="1">
         <v>0.59380502673888302</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <f>AVERAGE(G2:I2)</f>
         <v>0.58700289871942768</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>0.91175424443594</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>0.89046175428268404</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>0.67910575615158997</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <f t="shared" ref="F3:F13" si="0">AVERAGE(C3:E3)</f>
         <v>0.8271072516234047</v>
       </c>
@@ -1028,28 +1037,28 @@
       <c r="I3" s="1">
         <v>0.34073512504617598</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <f t="shared" ref="J3:J13" si="1">AVERAGE(G3:I3)</f>
         <v>0.35967300645431166</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>0.92011169386062497</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>0.89958715980887505</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>0.88036678148685399</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <f t="shared" si="0"/>
         <v>0.90002187838545133</v>
       </c>
@@ -1062,28 +1071,28 @@
       <c r="I4" s="1">
         <v>0.71003659528354601</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <f t="shared" si="1"/>
         <v>0.70098709246310242</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>0.95251569171056205</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>0.92496136827902098</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>0.94054042525112702</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <f t="shared" si="0"/>
         <v>0.93933916174690335</v>
       </c>
@@ -1096,28 +1105,28 @@
       <c r="I5" s="1">
         <v>0.64816377113897095</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <f t="shared" si="1"/>
         <v>0.61976563848094901</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>0.95619102192090599</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>0.95961148256541395</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>0.90538616253053295</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <f t="shared" si="0"/>
         <v>0.94039622233895104</v>
       </c>
@@ -1130,28 +1139,28 @@
       <c r="I6" s="1">
         <v>0.462060210240545</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <f t="shared" si="1"/>
         <v>0.42084620398633471</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>0.96824320411870102</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>0.96103906980031495</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>0.96128313546581201</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <f t="shared" si="0"/>
         <v>0.96352180312827596</v>
       </c>
@@ -1164,28 +1173,28 @@
       <c r="I7" s="1">
         <v>0.37763374690061802</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <f t="shared" si="1"/>
         <v>0.37728921910987201</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>0.93236734052329295</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>0.92756628529462104</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>0.87306495312216903</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <f t="shared" si="0"/>
         <v>0.9109995263133609</v>
       </c>
@@ -1198,28 +1207,28 @@
       <c r="I8" s="1">
         <v>0.88354917930098797</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <f t="shared" si="1"/>
         <v>0.81736590206193005</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>0.98318903240838096</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>0.98393597394509003</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>0.97691546196351897</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <f t="shared" si="0"/>
         <v>0.98134682277232999</v>
       </c>
@@ -1232,28 +1241,28 @@
       <c r="I9" s="1">
         <v>0.25770093855128301</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <f t="shared" si="1"/>
         <v>0.256483151119905</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>0.88743389777322101</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>0.90070157434061704</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>0.835935839151416</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <f t="shared" si="0"/>
         <v>0.87469043708841809</v>
       </c>
@@ -1266,28 +1275,28 @@
       <c r="I10" s="1">
         <v>0.48373034741116799</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <f t="shared" si="1"/>
         <v>0.43421260293524</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>0.91232631896454097</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>0.85118807173833699</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>0.88176370339103305</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <f t="shared" si="0"/>
         <v>0.88175936469797023</v>
       </c>
@@ -1300,28 +1309,28 @@
       <c r="I11" s="1">
         <v>0.30911008303335002</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <f t="shared" si="1"/>
         <v>0.34713369392143839</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>0.94993721148629295</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>0.95989447927501304</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>0.95377188035684701</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <f t="shared" si="0"/>
         <v>0.95453452370605107</v>
       </c>
@@ -1334,28 +1343,28 @@
       <c r="I12" s="1">
         <v>0.342795042945718</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <f t="shared" si="1"/>
         <v>0.30909461808059829</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>0.95317795535904004</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>0.94444496000522205</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>0.94525271931351795</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <f t="shared" si="0"/>
         <v>0.94762521155925994</v>
       </c>
@@ -1368,43 +1377,43 @@
       <c r="I13" s="1">
         <v>0.567017024042477</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <f t="shared" si="1"/>
         <v>0.52443904773818695</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <f>AVERAGE(C2:E13)</f>
         <v>0.92010083901442619</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="1">
         <f>_xlfn.STDEV.S(C2:E13)</f>
         <v>5.5738408386655627E-2</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="1">
         <f>AVERAGE(G2:I13)</f>
         <v>0.47952442292260794</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="1">
         <f>_xlfn.STDEV.S(G2:I13)</f>
         <v>0.16903520709507738</v>
       </c>
